--- a/docs/downloads/04/tbl_cm_educ_sex_marovoay_maroala.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_sex_marovoay_maroala.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,12 +397,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>9.1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -463,14 +457,8 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>4.5</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -555,7 +543,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D9">
@@ -647,7 +635,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D13">
@@ -674,10 +662,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E14">
-        <v>16.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -739,37 +727,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D17">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E17">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18">
-        <v>0.5</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_cm_educ_sex_marovoay_maroala.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_sex_marovoay_maroala.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,7 +394,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D6">
@@ -566,7 +566,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D10">
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="E14">
-        <v>16</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="15">
@@ -681,14 +681,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D15">
-        <v>199</v>
+        <v>59</v>
       </c>
       <c r="E15">
-        <v>49.1</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="16">
@@ -704,14 +704,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D16">
-        <v>104</v>
+        <v>199</v>
       </c>
       <c r="E16">
-        <v>25.7</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="17">
@@ -727,13 +727,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>104</v>
+      </c>
+      <c r="E17">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
-      <c r="D17">
+      <c r="D18">
         <v>37</v>
       </c>
-      <c r="E17">
+      <c r="E18">
         <v>9.1</v>
       </c>
     </row>
